--- a/db/A7XLK-2101-PublicService.xlsx
+++ b/db/A7XLK-2101-PublicService.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D004CD-16B4-184D-8C15-ED00C2968142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E664E7-34A6-3A4D-9F9A-4A0576720451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="7700" windowWidth="33240" windowHeight="16820" xr2:uid="{7DF87556-02EF-1D4C-B521-3FC679870A01}"/>
+    <workbookView xWindow="4120" yWindow="6220" windowWidth="33240" windowHeight="16820" xr2:uid="{7DF87556-02EF-1D4C-B521-3FC679870A01}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -666,49 +666,6 @@
     <t>210</t>
   </si>
   <si>
-    <t>中華電信 龜山文化門市</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>桃園市龜山區文化二路</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>38-8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>號</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>03-327-0303</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>12:00 - 21:00</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>fig/A7XLK-212-中華電信.jpeg</t>
   </si>
   <si>
@@ -2746,6 +2703,22 @@
   <si>
     <t>fig/A7XLK-211-文欣國小.jpeg</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中華電信龜山長庚服務中心</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區復興一路310號</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>080-008-0123</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:00 - 20:30</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2862,7 +2835,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2877,6 +2850,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3233,333 +3207,333 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>258</v>
-      </c>
       <c r="H3" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>264</v>
-      </c>
       <c r="H4" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>283</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="G7" s="8" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="H8" s="7" t="s">
         <v>210</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>219</v>
-      </c>
       <c r="H9" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>224</v>
-      </c>
       <c r="H10" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>230</v>
-      </c>
       <c r="H11" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>296</v>
-      </c>
       <c r="G12" s="6" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>236</v>
-      </c>
       <c r="H13" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>242</v>
-      </c>
       <c r="H14" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="17">
       <c r="A15" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -3801,22 +3775,22 @@
         <v>69</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="G25" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>15</v>
@@ -3824,25 +3798,25 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="G26" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>15</v>
@@ -3850,25 +3824,25 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="G27" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>15</v>
@@ -3876,25 +3850,25 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="F28" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="G28" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>15</v>
@@ -3902,25 +3876,25 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="G29" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>15</v>
@@ -3928,22 +3902,22 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="G30" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>15</v>
@@ -3951,418 +3925,418 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="G31" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="G32" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>123</v>
-      </c>
       <c r="H32" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="G33" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>129</v>
-      </c>
       <c r="H33" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="G34" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>135</v>
-      </c>
       <c r="H34" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="F35" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="G35" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>142</v>
-      </c>
       <c r="H35" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="G36" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>148</v>
-      </c>
       <c r="H36" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="G37" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>154</v>
-      </c>
       <c r="H37" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="G38" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>160</v>
-      </c>
       <c r="H38" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="G39" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>166</v>
-      </c>
       <c r="H39" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="G40" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>172</v>
-      </c>
       <c r="H40" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="G41" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="H41" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="G42" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>184</v>
-      </c>
       <c r="H42" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="G43" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>190</v>
-      </c>
       <c r="H43" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="G44" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>196</v>
-      </c>
       <c r="H44" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="G45" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>202</v>
-      </c>
       <c r="H45" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F46" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="G46" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>208</v>
-      </c>
       <c r="H46" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/db/A7XLK-2101-PublicService.xlsx
+++ b/db/A7XLK-2101-PublicService.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10313"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E664E7-34A6-3A4D-9F9A-4A0576720451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4B2EB0-BDA0-244E-90E2-D39D2FD9093C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4120" yWindow="6220" windowWidth="33240" windowHeight="16820" xr2:uid="{7DF87556-02EF-1D4C-B521-3FC679870A01}"/>
+    <workbookView xWindow="880" yWindow="1180" windowWidth="27920" windowHeight="16820" xr2:uid="{7DF87556-02EF-1D4C-B521-3FC679870A01}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="309">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -2719,6 +2719,54 @@
   <si>
     <t>11:00 - 20:30</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>115</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>116</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>林口高級中學</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>壽山高級中學</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lksh.ntpc.edu.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.sssh.tyc.edu.tw/bin/home.php</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-211-林口高中.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-211-壽山高中.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區仁愛路二段173號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2600-9482</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">桃園市龜山區大同路23號 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-350-1778</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3166,7 +3214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9307F4ED-2E27-7E4C-8083-2201FF514F2E}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -3354,22 +3402,22 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>239</v>
+        <v>297</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>205</v>
+        <v>299</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>206</v>
+        <v>305</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>207</v>
+        <v>306</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>209</v>
+        <v>303</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>301</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>210</v>
@@ -3377,22 +3425,22 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>244</v>
+        <v>298</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>211</v>
+        <v>300</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>212</v>
+        <v>307</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>213</v>
+        <v>308</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>215</v>
+        <v>304</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>302</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>210</v>
@@ -3400,22 +3448,22 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>210</v>
@@ -3423,22 +3471,22 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>210</v>
@@ -3446,22 +3494,22 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>288</v>
+        <v>216</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>289</v>
+        <v>217</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>290</v>
+        <v>218</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>292</v>
+        <v>219</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>291</v>
+        <v>220</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>210</v>
@@ -3469,22 +3517,22 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>274</v>
+        <v>246</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>210</v>
@@ -3492,45 +3540,45 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>281</v>
+        <v>247</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>234</v>
+        <v>288</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>235</v>
+        <v>289</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>236</v>
+        <v>290</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>237</v>
+        <v>292</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>238</v>
+        <v>291</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="17">
+    <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>283</v>
+        <v>274</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>228</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>284</v>
+        <v>229</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>285</v>
+        <v>230</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>286</v>
+        <v>231</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>282</v>
+        <v>232</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>210</v>
@@ -3538,77 +3586,71 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>8</v>
+        <v>281</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>9</v>
+        <v>234</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>10</v>
+        <v>235</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>12</v>
+        <v>236</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>237</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="17">
       <c r="A17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>17</v>
+        <v>287</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>283</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>18</v>
+        <v>284</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>15</v>
+        <v>286</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>15</v>
@@ -3616,25 +3658,25 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>15</v>
@@ -3642,25 +3684,25 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>15</v>
@@ -3668,25 +3710,25 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>15</v>
@@ -3694,25 +3736,25 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>15</v>
@@ -3720,25 +3762,25 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>60</v>
+        <v>45</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>62</v>
+        <v>47</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>15</v>
@@ -3746,25 +3788,25 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>68</v>
+        <v>54</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>15</v>
@@ -3772,25 +3814,25 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>294</v>
+        <v>57</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>296</v>
+        <v>59</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>71</v>
+        <v>61</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>15</v>
@@ -3798,25 +3840,25 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>76</v>
+        <v>59</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>78</v>
+        <v>67</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>15</v>
@@ -3824,25 +3866,25 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>81</v>
+        <v>293</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>294</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>15</v>
@@ -3850,25 +3892,25 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>15</v>
@@ -3876,25 +3918,25 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>97</v>
+        <v>82</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>15</v>
@@ -3902,22 +3944,25 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>101</v>
+        <v>87</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>15</v>
@@ -3925,77 +3970,74 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>110</v>
+        <v>96</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>112</v>
+        <v>98</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>113</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>119</v>
+        <v>104</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>113</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>113</v>
@@ -4003,25 +4045,25 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>113</v>
@@ -4029,25 +4071,25 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>113</v>
@@ -4055,25 +4097,25 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>113</v>
@@ -4081,25 +4123,25 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>113</v>
@@ -4107,25 +4149,25 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>113</v>
@@ -4133,25 +4175,25 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>113</v>
@@ -4159,25 +4201,25 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>113</v>
@@ -4185,25 +4227,25 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>113</v>
@@ -4211,25 +4253,25 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>113</v>
@@ -4237,25 +4279,25 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>113</v>
@@ -4263,25 +4305,25 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>113</v>
@@ -4289,25 +4331,25 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>113</v>
@@ -4315,68 +4357,122 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>113</v>
       </c>
     </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H46">
-    <sortCondition ref="A2:A46"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H48">
+    <sortCondition ref="A2:A48"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G31" r:id="rId1" xr:uid="{0E2BDD09-F388-3C4E-88B2-0C2976D7E2AD}"/>
-    <hyperlink ref="G33" r:id="rId2" xr:uid="{202423FA-AE00-3B4B-9A2E-3ABEE3F17FC1}"/>
-    <hyperlink ref="G34" r:id="rId3" xr:uid="{02178641-BC52-FE4C-88FF-6E68AF2D7461}"/>
-    <hyperlink ref="G35" r:id="rId4" xr:uid="{B9158B92-B4DC-CE4E-B43C-3B1776A67F04}"/>
-    <hyperlink ref="G36" r:id="rId5" xr:uid="{E62A41D9-6F3C-254F-ABA3-0C7065B6AF1D}"/>
-    <hyperlink ref="G37" r:id="rId6" xr:uid="{3E67F505-15A2-EA4E-BE20-9A1B1C839282}"/>
-    <hyperlink ref="G38" r:id="rId7" xr:uid="{CCE6D3E0-4E9B-944A-8096-D88695DF4F2E}"/>
-    <hyperlink ref="G39" r:id="rId8" xr:uid="{1EBCF505-9B74-2A4C-B118-AB6D28279093}"/>
-    <hyperlink ref="G40" r:id="rId9" xr:uid="{28C9A489-9A93-8A48-AEB0-6ECC26550EAD}"/>
-    <hyperlink ref="G41" r:id="rId10" xr:uid="{FFAA74D8-6F0D-314D-8A3A-6A249BBED5F2}"/>
-    <hyperlink ref="G42" r:id="rId11" xr:uid="{B746E68D-B4DC-A542-9AF9-EE0B24B1B016}"/>
-    <hyperlink ref="G43" r:id="rId12" xr:uid="{2255613C-CC60-034E-A872-39E0B7FC3D75}"/>
-    <hyperlink ref="G44" r:id="rId13" xr:uid="{7D4BE070-BC2A-F640-AA24-55DB8607633C}"/>
-    <hyperlink ref="G45" r:id="rId14" xr:uid="{62F6C8D0-C319-E24B-82DB-583B28B01D6A}"/>
-    <hyperlink ref="G46" r:id="rId15" xr:uid="{C334E9F0-876C-BF48-B32A-3EF1783AF460}"/>
-    <hyperlink ref="G9" r:id="rId16" xr:uid="{F2BA78C2-850A-4A47-A4F1-5DCF7F273293}"/>
-    <hyperlink ref="G8" r:id="rId17" xr:uid="{436E7BCD-5514-BE44-A962-4391733E23CB}"/>
-    <hyperlink ref="G10" r:id="rId18" xr:uid="{123EFA42-8725-324A-BBCC-6C8EF94E13F0}"/>
-    <hyperlink ref="G11" r:id="rId19" xr:uid="{D3459DF9-68C3-AD4D-8120-D222882E4AD3}"/>
-    <hyperlink ref="G13" r:id="rId20" location="k" xr:uid="{59E1A23C-80ED-2B4F-AFE7-458A4282616D}"/>
-    <hyperlink ref="G14" r:id="rId21" xr:uid="{2CAE0BCF-2A2C-8142-AAFE-6DA57825F133}"/>
-    <hyperlink ref="G23" r:id="rId22" xr:uid="{AA3DA1D0-56F9-4E4C-93C6-CDCFE7FA56E2}"/>
-    <hyperlink ref="G24" r:id="rId23" xr:uid="{0C2EA970-4D01-2748-B88C-3C78E669DCE7}"/>
-    <hyperlink ref="G32" r:id="rId24" xr:uid="{091A8EB7-8C3F-F748-8014-F56861AC0817}"/>
+    <hyperlink ref="G33" r:id="rId1" xr:uid="{0E2BDD09-F388-3C4E-88B2-0C2976D7E2AD}"/>
+    <hyperlink ref="G35" r:id="rId2" xr:uid="{202423FA-AE00-3B4B-9A2E-3ABEE3F17FC1}"/>
+    <hyperlink ref="G36" r:id="rId3" xr:uid="{02178641-BC52-FE4C-88FF-6E68AF2D7461}"/>
+    <hyperlink ref="G37" r:id="rId4" xr:uid="{B9158B92-B4DC-CE4E-B43C-3B1776A67F04}"/>
+    <hyperlink ref="G38" r:id="rId5" xr:uid="{E62A41D9-6F3C-254F-ABA3-0C7065B6AF1D}"/>
+    <hyperlink ref="G39" r:id="rId6" xr:uid="{3E67F505-15A2-EA4E-BE20-9A1B1C839282}"/>
+    <hyperlink ref="G40" r:id="rId7" xr:uid="{CCE6D3E0-4E9B-944A-8096-D88695DF4F2E}"/>
+    <hyperlink ref="G41" r:id="rId8" xr:uid="{1EBCF505-9B74-2A4C-B118-AB6D28279093}"/>
+    <hyperlink ref="G42" r:id="rId9" xr:uid="{28C9A489-9A93-8A48-AEB0-6ECC26550EAD}"/>
+    <hyperlink ref="G43" r:id="rId10" xr:uid="{FFAA74D8-6F0D-314D-8A3A-6A249BBED5F2}"/>
+    <hyperlink ref="G44" r:id="rId11" xr:uid="{B746E68D-B4DC-A542-9AF9-EE0B24B1B016}"/>
+    <hyperlink ref="G45" r:id="rId12" xr:uid="{2255613C-CC60-034E-A872-39E0B7FC3D75}"/>
+    <hyperlink ref="G46" r:id="rId13" xr:uid="{7D4BE070-BC2A-F640-AA24-55DB8607633C}"/>
+    <hyperlink ref="G47" r:id="rId14" xr:uid="{62F6C8D0-C319-E24B-82DB-583B28B01D6A}"/>
+    <hyperlink ref="G48" r:id="rId15" xr:uid="{C334E9F0-876C-BF48-B32A-3EF1783AF460}"/>
+    <hyperlink ref="G11" r:id="rId16" xr:uid="{F2BA78C2-850A-4A47-A4F1-5DCF7F273293}"/>
+    <hyperlink ref="G10" r:id="rId17" xr:uid="{436E7BCD-5514-BE44-A962-4391733E23CB}"/>
+    <hyperlink ref="G12" r:id="rId18" xr:uid="{123EFA42-8725-324A-BBCC-6C8EF94E13F0}"/>
+    <hyperlink ref="G13" r:id="rId19" xr:uid="{D3459DF9-68C3-AD4D-8120-D222882E4AD3}"/>
+    <hyperlink ref="G15" r:id="rId20" location="k" xr:uid="{59E1A23C-80ED-2B4F-AFE7-458A4282616D}"/>
+    <hyperlink ref="G16" r:id="rId21" xr:uid="{2CAE0BCF-2A2C-8142-AAFE-6DA57825F133}"/>
+    <hyperlink ref="G25" r:id="rId22" xr:uid="{AA3DA1D0-56F9-4E4C-93C6-CDCFE7FA56E2}"/>
+    <hyperlink ref="G26" r:id="rId23" xr:uid="{0C2EA970-4D01-2748-B88C-3C78E669DCE7}"/>
+    <hyperlink ref="G34" r:id="rId24" xr:uid="{091A8EB7-8C3F-F748-8014-F56861AC0817}"/>
     <hyperlink ref="G2" r:id="rId25" xr:uid="{1E13781E-B861-354C-817E-92F030A541AD}"/>
     <hyperlink ref="G3" r:id="rId26" xr:uid="{2E356582-CD9B-294A-A59D-AE8B3F4EF906}"/>
     <hyperlink ref="G4" r:id="rId27" xr:uid="{D2631B09-11CF-9D49-BC2B-00012E8636BE}"/>
     <hyperlink ref="G5" r:id="rId28" xr:uid="{F69F7CDE-C350-4540-93FE-EFE72685550A}"/>
     <hyperlink ref="G7" r:id="rId29" location="gsc.tab=0" xr:uid="{5F9651E1-CC47-9F46-A35D-913CD10FA98B}"/>
     <hyperlink ref="G6" r:id="rId30" xr:uid="{F67F1519-6345-4847-8D18-FD785616B520}"/>
-    <hyperlink ref="G15" r:id="rId31" xr:uid="{255D97BB-DCE4-A74C-93F3-9E02876D1DEF}"/>
-    <hyperlink ref="G12" r:id="rId32" xr:uid="{571D6DC6-9B82-E444-99A9-0656019A52AA}"/>
+    <hyperlink ref="G17" r:id="rId31" xr:uid="{255D97BB-DCE4-A74C-93F3-9E02876D1DEF}"/>
+    <hyperlink ref="G14" r:id="rId32" xr:uid="{571D6DC6-9B82-E444-99A9-0656019A52AA}"/>
+    <hyperlink ref="G8" r:id="rId33" xr:uid="{8C9B77CC-6EB2-FF4D-A768-2BDA18294FE0}"/>
+    <hyperlink ref="G9" r:id="rId34" xr:uid="{BE2C565E-6EE5-3644-8DCD-2FDE7E6A1B7D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-2101-PublicService.xlsx
+++ b/db/A7XLK-2101-PublicService.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4B2EB0-BDA0-244E-90E2-D39D2FD9093C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D20C8CE-F80C-5247-A3D7-E5C3A102F34A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="1180" windowWidth="27920" windowHeight="16820" xr2:uid="{7DF87556-02EF-1D4C-B521-3FC679870A01}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="314">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -2766,6 +2766,26 @@
   </si>
   <si>
     <t>03-350-1778</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>117</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>樂善國小附設幼兒園</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區樂善里11鄰樂安街71號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-328-1002#910</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www4.leses.tyc.edu.tw/happy/preschool/</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3214,7 +3234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9307F4ED-2E27-7E4C-8083-2201FF514F2E}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -3630,53 +3650,50 @@
         <v>210</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" ht="17">
       <c r="A18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>9</v>
+        <v>309</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>310</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>10</v>
+        <v>311</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>12</v>
+        <v>312</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>15</v>
+        <v>219</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>15</v>
@@ -3684,25 +3701,25 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>15</v>
@@ -3710,25 +3727,25 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>15</v>
@@ -3736,25 +3753,25 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>15</v>
@@ -3762,25 +3779,25 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>15</v>
@@ -3788,25 +3805,25 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>53</v>
+        <v>45</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>15</v>
@@ -3814,25 +3831,25 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>62</v>
+        <v>54</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>15</v>
@@ -3840,25 +3857,25 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>15</v>
@@ -3866,25 +3883,25 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>294</v>
+        <v>64</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>296</v>
+        <v>59</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>15</v>
@@ -3892,25 +3909,25 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>74</v>
+        <v>293</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>294</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>75</v>
+        <v>295</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>76</v>
+        <v>296</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>15</v>
@@ -3918,25 +3935,25 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>15</v>
@@ -3944,25 +3961,25 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>15</v>
@@ -3970,25 +3987,25 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>97</v>
+        <v>89</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>15</v>
@@ -3996,22 +4013,25 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>15</v>
@@ -4019,51 +4039,48 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>112</v>
+        <v>104</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>113</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>113</v>
@@ -4071,25 +4088,25 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>113</v>
@@ -4097,25 +4114,25 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>113</v>
@@ -4123,25 +4140,25 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>113</v>
@@ -4149,25 +4166,25 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>113</v>
@@ -4175,25 +4192,25 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>113</v>
@@ -4201,25 +4218,25 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>113</v>
@@ -4227,25 +4244,25 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>113</v>
@@ -4253,25 +4270,25 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>113</v>
@@ -4279,25 +4296,25 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>113</v>
@@ -4305,25 +4322,25 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>113</v>
@@ -4331,25 +4348,25 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>113</v>
@@ -4357,25 +4374,25 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>113</v>
@@ -4383,25 +4400,25 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>113</v>
@@ -4409,60 +4426,86 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>113</v>
       </c>
     </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H48">
-    <sortCondition ref="A2:A48"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H49">
+    <sortCondition ref="A2:A49"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G33" r:id="rId1" xr:uid="{0E2BDD09-F388-3C4E-88B2-0C2976D7E2AD}"/>
-    <hyperlink ref="G35" r:id="rId2" xr:uid="{202423FA-AE00-3B4B-9A2E-3ABEE3F17FC1}"/>
-    <hyperlink ref="G36" r:id="rId3" xr:uid="{02178641-BC52-FE4C-88FF-6E68AF2D7461}"/>
-    <hyperlink ref="G37" r:id="rId4" xr:uid="{B9158B92-B4DC-CE4E-B43C-3B1776A67F04}"/>
-    <hyperlink ref="G38" r:id="rId5" xr:uid="{E62A41D9-6F3C-254F-ABA3-0C7065B6AF1D}"/>
-    <hyperlink ref="G39" r:id="rId6" xr:uid="{3E67F505-15A2-EA4E-BE20-9A1B1C839282}"/>
-    <hyperlink ref="G40" r:id="rId7" xr:uid="{CCE6D3E0-4E9B-944A-8096-D88695DF4F2E}"/>
-    <hyperlink ref="G41" r:id="rId8" xr:uid="{1EBCF505-9B74-2A4C-B118-AB6D28279093}"/>
-    <hyperlink ref="G42" r:id="rId9" xr:uid="{28C9A489-9A93-8A48-AEB0-6ECC26550EAD}"/>
-    <hyperlink ref="G43" r:id="rId10" xr:uid="{FFAA74D8-6F0D-314D-8A3A-6A249BBED5F2}"/>
-    <hyperlink ref="G44" r:id="rId11" xr:uid="{B746E68D-B4DC-A542-9AF9-EE0B24B1B016}"/>
-    <hyperlink ref="G45" r:id="rId12" xr:uid="{2255613C-CC60-034E-A872-39E0B7FC3D75}"/>
-    <hyperlink ref="G46" r:id="rId13" xr:uid="{7D4BE070-BC2A-F640-AA24-55DB8607633C}"/>
-    <hyperlink ref="G47" r:id="rId14" xr:uid="{62F6C8D0-C319-E24B-82DB-583B28B01D6A}"/>
-    <hyperlink ref="G48" r:id="rId15" xr:uid="{C334E9F0-876C-BF48-B32A-3EF1783AF460}"/>
+    <hyperlink ref="G34" r:id="rId1" xr:uid="{0E2BDD09-F388-3C4E-88B2-0C2976D7E2AD}"/>
+    <hyperlink ref="G36" r:id="rId2" xr:uid="{202423FA-AE00-3B4B-9A2E-3ABEE3F17FC1}"/>
+    <hyperlink ref="G37" r:id="rId3" xr:uid="{02178641-BC52-FE4C-88FF-6E68AF2D7461}"/>
+    <hyperlink ref="G38" r:id="rId4" xr:uid="{B9158B92-B4DC-CE4E-B43C-3B1776A67F04}"/>
+    <hyperlink ref="G39" r:id="rId5" xr:uid="{E62A41D9-6F3C-254F-ABA3-0C7065B6AF1D}"/>
+    <hyperlink ref="G40" r:id="rId6" xr:uid="{3E67F505-15A2-EA4E-BE20-9A1B1C839282}"/>
+    <hyperlink ref="G41" r:id="rId7" xr:uid="{CCE6D3E0-4E9B-944A-8096-D88695DF4F2E}"/>
+    <hyperlink ref="G42" r:id="rId8" xr:uid="{1EBCF505-9B74-2A4C-B118-AB6D28279093}"/>
+    <hyperlink ref="G43" r:id="rId9" xr:uid="{28C9A489-9A93-8A48-AEB0-6ECC26550EAD}"/>
+    <hyperlink ref="G44" r:id="rId10" xr:uid="{FFAA74D8-6F0D-314D-8A3A-6A249BBED5F2}"/>
+    <hyperlink ref="G45" r:id="rId11" xr:uid="{B746E68D-B4DC-A542-9AF9-EE0B24B1B016}"/>
+    <hyperlink ref="G46" r:id="rId12" xr:uid="{2255613C-CC60-034E-A872-39E0B7FC3D75}"/>
+    <hyperlink ref="G47" r:id="rId13" xr:uid="{7D4BE070-BC2A-F640-AA24-55DB8607633C}"/>
+    <hyperlink ref="G48" r:id="rId14" xr:uid="{62F6C8D0-C319-E24B-82DB-583B28B01D6A}"/>
+    <hyperlink ref="G49" r:id="rId15" xr:uid="{C334E9F0-876C-BF48-B32A-3EF1783AF460}"/>
     <hyperlink ref="G11" r:id="rId16" xr:uid="{F2BA78C2-850A-4A47-A4F1-5DCF7F273293}"/>
     <hyperlink ref="G10" r:id="rId17" xr:uid="{436E7BCD-5514-BE44-A962-4391733E23CB}"/>
     <hyperlink ref="G12" r:id="rId18" xr:uid="{123EFA42-8725-324A-BBCC-6C8EF94E13F0}"/>
     <hyperlink ref="G13" r:id="rId19" xr:uid="{D3459DF9-68C3-AD4D-8120-D222882E4AD3}"/>
     <hyperlink ref="G15" r:id="rId20" location="k" xr:uid="{59E1A23C-80ED-2B4F-AFE7-458A4282616D}"/>
     <hyperlink ref="G16" r:id="rId21" xr:uid="{2CAE0BCF-2A2C-8142-AAFE-6DA57825F133}"/>
-    <hyperlink ref="G25" r:id="rId22" xr:uid="{AA3DA1D0-56F9-4E4C-93C6-CDCFE7FA56E2}"/>
-    <hyperlink ref="G26" r:id="rId23" xr:uid="{0C2EA970-4D01-2748-B88C-3C78E669DCE7}"/>
-    <hyperlink ref="G34" r:id="rId24" xr:uid="{091A8EB7-8C3F-F748-8014-F56861AC0817}"/>
+    <hyperlink ref="G26" r:id="rId22" xr:uid="{AA3DA1D0-56F9-4E4C-93C6-CDCFE7FA56E2}"/>
+    <hyperlink ref="G27" r:id="rId23" xr:uid="{0C2EA970-4D01-2748-B88C-3C78E669DCE7}"/>
+    <hyperlink ref="G35" r:id="rId24" xr:uid="{091A8EB7-8C3F-F748-8014-F56861AC0817}"/>
     <hyperlink ref="G2" r:id="rId25" xr:uid="{1E13781E-B861-354C-817E-92F030A541AD}"/>
     <hyperlink ref="G3" r:id="rId26" xr:uid="{2E356582-CD9B-294A-A59D-AE8B3F4EF906}"/>
     <hyperlink ref="G4" r:id="rId27" xr:uid="{D2631B09-11CF-9D49-BC2B-00012E8636BE}"/>
@@ -4473,6 +4516,7 @@
     <hyperlink ref="G14" r:id="rId32" xr:uid="{571D6DC6-9B82-E444-99A9-0656019A52AA}"/>
     <hyperlink ref="G8" r:id="rId33" xr:uid="{8C9B77CC-6EB2-FF4D-A768-2BDA18294FE0}"/>
     <hyperlink ref="G9" r:id="rId34" xr:uid="{BE2C565E-6EE5-3644-8DCD-2FDE7E6A1B7D}"/>
+    <hyperlink ref="G18" r:id="rId35" xr:uid="{283216B3-6D1E-BC47-9A4F-156BCBCEA991}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-2101-PublicService.xlsx
+++ b/db/A7XLK-2101-PublicService.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10313"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10410"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D20C8CE-F80C-5247-A3D7-E5C3A102F34A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFC7F96-16F9-8046-91F4-A0FC98A98FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="1180" windowWidth="27920" windowHeight="16820" xr2:uid="{7DF87556-02EF-1D4C-B521-3FC679870A01}"/>
+    <workbookView xWindow="6380" yWindow="500" windowWidth="27920" windowHeight="16820" xr2:uid="{7DF87556-02EF-1D4C-B521-3FC679870A01}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="331">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -2786,6 +2786,158 @@
   </si>
   <si>
     <t>http://www4.leses.tyc.edu.tw/happy/preschool/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>216</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>217</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>218</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>龜山文青郵政代辦所</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園市龜山區文青路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:00-17:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>龜山長庚大學郵局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>龜山樂善郵局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-328-2459</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-211-8633</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園市龜山區文化一路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>259</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園市龜山區復興街</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.post.gov.tw/post/internet/I_location/index_post.jsp?prsb_no=012136-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>週一至週五 郵務:08:30-17:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.post.gov.tw/post/internet/I_location/index_post.jsp?prsb_no=012117-6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 週一至週五 郵務:08:30-17:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-212-郵局代辦所.jpeg</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2903,7 +3055,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2919,6 +3071,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3234,7 +3387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9307F4ED-2E27-7E4C-8083-2201FF514F2E}">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -3857,25 +4010,19 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>56</v>
+        <v>314</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>57</v>
+        <v>317</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>59</v>
+        <v>318</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>60</v>
+        <v>319</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>62</v>
+        <v>330</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>15</v>
@@ -3883,25 +4030,25 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>63</v>
+        <v>315</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>64</v>
+        <v>320</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>65</v>
+        <v>324</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>59</v>
+        <v>323</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>66</v>
+        <v>327</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>68</v>
+        <v>54</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>326</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>15</v>
@@ -3909,25 +4056,25 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>69</v>
+        <v>316</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>294</v>
+        <v>321</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>325</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>296</v>
+        <v>322</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>329</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>71</v>
+        <v>54</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>328</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>15</v>
@@ -3935,25 +4082,25 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>76</v>
+        <v>59</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>78</v>
+        <v>61</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>15</v>
@@ -3961,25 +4108,25 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>83</v>
+        <v>59</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>85</v>
+        <v>67</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>15</v>
@@ -3987,25 +4134,25 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>88</v>
+        <v>293</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>294</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>89</v>
+        <v>295</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>90</v>
+        <v>296</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>15</v>
@@ -4013,25 +4160,25 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>97</v>
+        <v>75</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>15</v>
@@ -4039,22 +4186,25 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>101</v>
+        <v>80</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>15</v>
@@ -4062,103 +4212,100 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>112</v>
+        <v>91</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>113</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>110</v>
+        <v>96</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>119</v>
+        <v>98</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>113</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>125</v>
+        <v>104</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>113</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>113</v>
@@ -4166,25 +4313,25 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>113</v>
@@ -4192,25 +4339,25 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>113</v>
@@ -4218,25 +4365,25 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>113</v>
@@ -4244,25 +4391,25 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>113</v>
@@ -4270,25 +4417,25 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>113</v>
@@ -4296,25 +4443,25 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>113</v>
@@ -4322,25 +4469,25 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>113</v>
@@ -4348,25 +4495,25 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>113</v>
@@ -4374,25 +4521,25 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>113</v>
@@ -4400,25 +4547,25 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>113</v>
@@ -4426,25 +4573,25 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>113</v>
@@ -4452,60 +4599,138 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>113</v>
       </c>
     </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H49">
-    <sortCondition ref="A2:A49"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H52">
+    <sortCondition ref="A2:A52"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G34" r:id="rId1" xr:uid="{0E2BDD09-F388-3C4E-88B2-0C2976D7E2AD}"/>
-    <hyperlink ref="G36" r:id="rId2" xr:uid="{202423FA-AE00-3B4B-9A2E-3ABEE3F17FC1}"/>
-    <hyperlink ref="G37" r:id="rId3" xr:uid="{02178641-BC52-FE4C-88FF-6E68AF2D7461}"/>
-    <hyperlink ref="G38" r:id="rId4" xr:uid="{B9158B92-B4DC-CE4E-B43C-3B1776A67F04}"/>
-    <hyperlink ref="G39" r:id="rId5" xr:uid="{E62A41D9-6F3C-254F-ABA3-0C7065B6AF1D}"/>
-    <hyperlink ref="G40" r:id="rId6" xr:uid="{3E67F505-15A2-EA4E-BE20-9A1B1C839282}"/>
-    <hyperlink ref="G41" r:id="rId7" xr:uid="{CCE6D3E0-4E9B-944A-8096-D88695DF4F2E}"/>
-    <hyperlink ref="G42" r:id="rId8" xr:uid="{1EBCF505-9B74-2A4C-B118-AB6D28279093}"/>
-    <hyperlink ref="G43" r:id="rId9" xr:uid="{28C9A489-9A93-8A48-AEB0-6ECC26550EAD}"/>
-    <hyperlink ref="G44" r:id="rId10" xr:uid="{FFAA74D8-6F0D-314D-8A3A-6A249BBED5F2}"/>
-    <hyperlink ref="G45" r:id="rId11" xr:uid="{B746E68D-B4DC-A542-9AF9-EE0B24B1B016}"/>
-    <hyperlink ref="G46" r:id="rId12" xr:uid="{2255613C-CC60-034E-A872-39E0B7FC3D75}"/>
-    <hyperlink ref="G47" r:id="rId13" xr:uid="{7D4BE070-BC2A-F640-AA24-55DB8607633C}"/>
-    <hyperlink ref="G48" r:id="rId14" xr:uid="{62F6C8D0-C319-E24B-82DB-583B28B01D6A}"/>
-    <hyperlink ref="G49" r:id="rId15" xr:uid="{C334E9F0-876C-BF48-B32A-3EF1783AF460}"/>
+    <hyperlink ref="G37" r:id="rId1" xr:uid="{0E2BDD09-F388-3C4E-88B2-0C2976D7E2AD}"/>
+    <hyperlink ref="G39" r:id="rId2" xr:uid="{202423FA-AE00-3B4B-9A2E-3ABEE3F17FC1}"/>
+    <hyperlink ref="G40" r:id="rId3" xr:uid="{02178641-BC52-FE4C-88FF-6E68AF2D7461}"/>
+    <hyperlink ref="G41" r:id="rId4" xr:uid="{B9158B92-B4DC-CE4E-B43C-3B1776A67F04}"/>
+    <hyperlink ref="G42" r:id="rId5" xr:uid="{E62A41D9-6F3C-254F-ABA3-0C7065B6AF1D}"/>
+    <hyperlink ref="G43" r:id="rId6" xr:uid="{3E67F505-15A2-EA4E-BE20-9A1B1C839282}"/>
+    <hyperlink ref="G44" r:id="rId7" xr:uid="{CCE6D3E0-4E9B-944A-8096-D88695DF4F2E}"/>
+    <hyperlink ref="G45" r:id="rId8" xr:uid="{1EBCF505-9B74-2A4C-B118-AB6D28279093}"/>
+    <hyperlink ref="G46" r:id="rId9" xr:uid="{28C9A489-9A93-8A48-AEB0-6ECC26550EAD}"/>
+    <hyperlink ref="G47" r:id="rId10" xr:uid="{FFAA74D8-6F0D-314D-8A3A-6A249BBED5F2}"/>
+    <hyperlink ref="G48" r:id="rId11" xr:uid="{B746E68D-B4DC-A542-9AF9-EE0B24B1B016}"/>
+    <hyperlink ref="G49" r:id="rId12" xr:uid="{2255613C-CC60-034E-A872-39E0B7FC3D75}"/>
+    <hyperlink ref="G50" r:id="rId13" xr:uid="{7D4BE070-BC2A-F640-AA24-55DB8607633C}"/>
+    <hyperlink ref="G51" r:id="rId14" xr:uid="{62F6C8D0-C319-E24B-82DB-583B28B01D6A}"/>
+    <hyperlink ref="G52" r:id="rId15" xr:uid="{C334E9F0-876C-BF48-B32A-3EF1783AF460}"/>
     <hyperlink ref="G11" r:id="rId16" xr:uid="{F2BA78C2-850A-4A47-A4F1-5DCF7F273293}"/>
     <hyperlink ref="G10" r:id="rId17" xr:uid="{436E7BCD-5514-BE44-A962-4391733E23CB}"/>
     <hyperlink ref="G12" r:id="rId18" xr:uid="{123EFA42-8725-324A-BBCC-6C8EF94E13F0}"/>
     <hyperlink ref="G13" r:id="rId19" xr:uid="{D3459DF9-68C3-AD4D-8120-D222882E4AD3}"/>
     <hyperlink ref="G15" r:id="rId20" location="k" xr:uid="{59E1A23C-80ED-2B4F-AFE7-458A4282616D}"/>
     <hyperlink ref="G16" r:id="rId21" xr:uid="{2CAE0BCF-2A2C-8142-AAFE-6DA57825F133}"/>
-    <hyperlink ref="G26" r:id="rId22" xr:uid="{AA3DA1D0-56F9-4E4C-93C6-CDCFE7FA56E2}"/>
-    <hyperlink ref="G27" r:id="rId23" xr:uid="{0C2EA970-4D01-2748-B88C-3C78E669DCE7}"/>
-    <hyperlink ref="G35" r:id="rId24" xr:uid="{091A8EB7-8C3F-F748-8014-F56861AC0817}"/>
+    <hyperlink ref="G29" r:id="rId22" xr:uid="{AA3DA1D0-56F9-4E4C-93C6-CDCFE7FA56E2}"/>
+    <hyperlink ref="G30" r:id="rId23" xr:uid="{0C2EA970-4D01-2748-B88C-3C78E669DCE7}"/>
+    <hyperlink ref="G38" r:id="rId24" xr:uid="{091A8EB7-8C3F-F748-8014-F56861AC0817}"/>
     <hyperlink ref="G2" r:id="rId25" xr:uid="{1E13781E-B861-354C-817E-92F030A541AD}"/>
     <hyperlink ref="G3" r:id="rId26" xr:uid="{2E356582-CD9B-294A-A59D-AE8B3F4EF906}"/>
     <hyperlink ref="G4" r:id="rId27" xr:uid="{D2631B09-11CF-9D49-BC2B-00012E8636BE}"/>
@@ -4517,6 +4742,8 @@
     <hyperlink ref="G8" r:id="rId33" xr:uid="{8C9B77CC-6EB2-FF4D-A768-2BDA18294FE0}"/>
     <hyperlink ref="G9" r:id="rId34" xr:uid="{BE2C565E-6EE5-3644-8DCD-2FDE7E6A1B7D}"/>
     <hyperlink ref="G18" r:id="rId35" xr:uid="{283216B3-6D1E-BC47-9A4F-156BCBCEA991}"/>
+    <hyperlink ref="G27" r:id="rId36" xr:uid="{51347FCF-C6E8-A045-84B3-CCBE0B46DD99}"/>
+    <hyperlink ref="G28" r:id="rId37" xr:uid="{1E9157DD-7F86-1D42-8A0B-E535C7309FE9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-2101-PublicService.xlsx
+++ b/db/A7XLK-2101-PublicService.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10520"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFC7F96-16F9-8046-91F4-A0FC98A98FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4134D3D1-C593-884E-AC29-A5D6BF278E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6380" yWindow="500" windowWidth="27920" windowHeight="16820" xr2:uid="{7DF87556-02EF-1D4C-B521-3FC679870A01}"/>
+    <workbookView xWindow="20" yWindow="500" windowWidth="27920" windowHeight="16820" xr2:uid="{7DF87556-02EF-1D4C-B521-3FC679870A01}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="338">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -2938,6 +2938,52 @@
   </si>
   <si>
     <t>fig/A7XLK-212-郵局代辦所.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>118</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>龜山地政事務所</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區自強南路105號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-359-6480</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>星期一至星期五</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 08:00 - 17:00</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.guishan-land.tycg.gov.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-211-地政事務所.png</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3387,7 +3433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9307F4ED-2E27-7E4C-8083-2201FF514F2E}">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -3506,22 +3552,25 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>221</v>
+        <v>331</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>262</v>
+        <v>332</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>263</v>
+        <v>333</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>278</v>
+        <v>334</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>335</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>265</v>
+        <v>337</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>210</v>
@@ -3529,22 +3578,22 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>210</v>
@@ -3552,22 +3601,22 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>210</v>
@@ -3575,22 +3624,22 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>297</v>
+        <v>233</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>305</v>
+        <v>267</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>306</v>
+        <v>268</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>303</v>
+        <v>270</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>210</v>
@@ -3598,22 +3647,22 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>210</v>
@@ -3621,22 +3670,22 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>205</v>
+        <v>300</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>206</v>
+        <v>307</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>207</v>
+        <v>308</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>209</v>
+        <v>304</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>302</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>210</v>
@@ -3644,22 +3693,22 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>210</v>
@@ -3667,22 +3716,22 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>210</v>
@@ -3690,22 +3739,22 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>210</v>
@@ -3713,22 +3762,22 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>288</v>
+        <v>222</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>289</v>
+        <v>223</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>290</v>
+        <v>224</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>292</v>
+        <v>225</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>291</v>
+        <v>226</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>210</v>
@@ -3736,22 +3785,22 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>228</v>
+        <v>288</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>229</v>
+        <v>289</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>231</v>
+        <v>292</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>232</v>
+        <v>291</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>210</v>
@@ -3759,45 +3808,45 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="17">
+    <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>283</v>
+        <v>281</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>234</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>284</v>
+        <v>235</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>285</v>
+        <v>236</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>210</v>
@@ -3805,74 +3854,71 @@
     </row>
     <row r="18" spans="1:8" ht="17">
       <c r="A18" s="1" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>311</v>
+        <v>284</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>312</v>
+        <v>285</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>219</v>
+        <v>286</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>313</v>
+        <v>282</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" ht="17">
       <c r="A19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>9</v>
+        <v>309</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>310</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>10</v>
+        <v>311</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>12</v>
+        <v>312</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>15</v>
+        <v>219</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>15</v>
@@ -3880,25 +3926,25 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>20</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>15</v>
@@ -3906,25 +3952,25 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>15</v>
@@ -3932,25 +3978,25 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>15</v>
@@ -3958,25 +4004,25 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>15</v>
@@ -3984,25 +4030,25 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>53</v>
+        <v>45</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>15</v>
@@ -4010,19 +4056,25 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>314</v>
+        <v>49</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>317</v>
+        <v>50</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>318</v>
+        <v>51</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>319</v>
+        <v>53</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>330</v>
+        <v>54</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>15</v>
@@ -4030,25 +4082,19 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>15</v>
@@ -4056,25 +4102,25 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G28" s="11" t="s">
-        <v>328</v>
+      <c r="G28" s="8" t="s">
+        <v>326</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>15</v>
@@ -4082,25 +4128,25 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>56</v>
+        <v>316</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>57</v>
+        <v>321</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>58</v>
+        <v>325</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>59</v>
+        <v>322</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>60</v>
+        <v>329</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>62</v>
+        <v>54</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>328</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>15</v>
@@ -4108,25 +4154,25 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>15</v>
@@ -4134,25 +4180,25 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>294</v>
+        <v>64</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>296</v>
+        <v>59</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>15</v>
@@ -4160,25 +4206,25 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>74</v>
+        <v>293</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>294</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>75</v>
+        <v>295</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>76</v>
+        <v>296</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>15</v>
@@ -4186,25 +4232,25 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>15</v>
@@ -4212,25 +4258,25 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>15</v>
@@ -4238,25 +4284,25 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>97</v>
+        <v>89</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>15</v>
@@ -4264,22 +4310,25 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>15</v>
@@ -4287,51 +4336,48 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>112</v>
+        <v>104</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>113</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>113</v>
@@ -4339,25 +4385,25 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>113</v>
@@ -4365,25 +4411,25 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>113</v>
@@ -4391,25 +4437,25 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>113</v>
@@ -4417,25 +4463,25 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>113</v>
@@ -4443,25 +4489,25 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>113</v>
@@ -4469,25 +4515,25 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>113</v>
@@ -4495,25 +4541,25 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>113</v>
@@ -4521,25 +4567,25 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>113</v>
@@ -4547,25 +4593,25 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>113</v>
@@ -4573,25 +4619,25 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>113</v>
@@ -4599,25 +4645,25 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>113</v>
@@ -4625,25 +4671,25 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>113</v>
@@ -4651,25 +4697,25 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>113</v>
@@ -4677,73 +4723,100 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>113</v>
       </c>
     </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H52">
-    <sortCondition ref="A2:A52"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H53">
+    <sortCondition ref="A2:A53"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G37" r:id="rId1" xr:uid="{0E2BDD09-F388-3C4E-88B2-0C2976D7E2AD}"/>
-    <hyperlink ref="G39" r:id="rId2" xr:uid="{202423FA-AE00-3B4B-9A2E-3ABEE3F17FC1}"/>
-    <hyperlink ref="G40" r:id="rId3" xr:uid="{02178641-BC52-FE4C-88FF-6E68AF2D7461}"/>
-    <hyperlink ref="G41" r:id="rId4" xr:uid="{B9158B92-B4DC-CE4E-B43C-3B1776A67F04}"/>
-    <hyperlink ref="G42" r:id="rId5" xr:uid="{E62A41D9-6F3C-254F-ABA3-0C7065B6AF1D}"/>
-    <hyperlink ref="G43" r:id="rId6" xr:uid="{3E67F505-15A2-EA4E-BE20-9A1B1C839282}"/>
-    <hyperlink ref="G44" r:id="rId7" xr:uid="{CCE6D3E0-4E9B-944A-8096-D88695DF4F2E}"/>
-    <hyperlink ref="G45" r:id="rId8" xr:uid="{1EBCF505-9B74-2A4C-B118-AB6D28279093}"/>
-    <hyperlink ref="G46" r:id="rId9" xr:uid="{28C9A489-9A93-8A48-AEB0-6ECC26550EAD}"/>
-    <hyperlink ref="G47" r:id="rId10" xr:uid="{FFAA74D8-6F0D-314D-8A3A-6A249BBED5F2}"/>
-    <hyperlink ref="G48" r:id="rId11" xr:uid="{B746E68D-B4DC-A542-9AF9-EE0B24B1B016}"/>
-    <hyperlink ref="G49" r:id="rId12" xr:uid="{2255613C-CC60-034E-A872-39E0B7FC3D75}"/>
-    <hyperlink ref="G50" r:id="rId13" xr:uid="{7D4BE070-BC2A-F640-AA24-55DB8607633C}"/>
-    <hyperlink ref="G51" r:id="rId14" xr:uid="{62F6C8D0-C319-E24B-82DB-583B28B01D6A}"/>
-    <hyperlink ref="G52" r:id="rId15" xr:uid="{C334E9F0-876C-BF48-B32A-3EF1783AF460}"/>
-    <hyperlink ref="G11" r:id="rId16" xr:uid="{F2BA78C2-850A-4A47-A4F1-5DCF7F273293}"/>
-    <hyperlink ref="G10" r:id="rId17" xr:uid="{436E7BCD-5514-BE44-A962-4391733E23CB}"/>
-    <hyperlink ref="G12" r:id="rId18" xr:uid="{123EFA42-8725-324A-BBCC-6C8EF94E13F0}"/>
-    <hyperlink ref="G13" r:id="rId19" xr:uid="{D3459DF9-68C3-AD4D-8120-D222882E4AD3}"/>
-    <hyperlink ref="G15" r:id="rId20" location="k" xr:uid="{59E1A23C-80ED-2B4F-AFE7-458A4282616D}"/>
-    <hyperlink ref="G16" r:id="rId21" xr:uid="{2CAE0BCF-2A2C-8142-AAFE-6DA57825F133}"/>
-    <hyperlink ref="G29" r:id="rId22" xr:uid="{AA3DA1D0-56F9-4E4C-93C6-CDCFE7FA56E2}"/>
-    <hyperlink ref="G30" r:id="rId23" xr:uid="{0C2EA970-4D01-2748-B88C-3C78E669DCE7}"/>
-    <hyperlink ref="G38" r:id="rId24" xr:uid="{091A8EB7-8C3F-F748-8014-F56861AC0817}"/>
+    <hyperlink ref="G38" r:id="rId1" xr:uid="{0E2BDD09-F388-3C4E-88B2-0C2976D7E2AD}"/>
+    <hyperlink ref="G40" r:id="rId2" xr:uid="{202423FA-AE00-3B4B-9A2E-3ABEE3F17FC1}"/>
+    <hyperlink ref="G41" r:id="rId3" xr:uid="{02178641-BC52-FE4C-88FF-6E68AF2D7461}"/>
+    <hyperlink ref="G42" r:id="rId4" xr:uid="{B9158B92-B4DC-CE4E-B43C-3B1776A67F04}"/>
+    <hyperlink ref="G43" r:id="rId5" xr:uid="{E62A41D9-6F3C-254F-ABA3-0C7065B6AF1D}"/>
+    <hyperlink ref="G44" r:id="rId6" xr:uid="{3E67F505-15A2-EA4E-BE20-9A1B1C839282}"/>
+    <hyperlink ref="G45" r:id="rId7" xr:uid="{CCE6D3E0-4E9B-944A-8096-D88695DF4F2E}"/>
+    <hyperlink ref="G46" r:id="rId8" xr:uid="{1EBCF505-9B74-2A4C-B118-AB6D28279093}"/>
+    <hyperlink ref="G47" r:id="rId9" xr:uid="{28C9A489-9A93-8A48-AEB0-6ECC26550EAD}"/>
+    <hyperlink ref="G48" r:id="rId10" xr:uid="{FFAA74D8-6F0D-314D-8A3A-6A249BBED5F2}"/>
+    <hyperlink ref="G49" r:id="rId11" xr:uid="{B746E68D-B4DC-A542-9AF9-EE0B24B1B016}"/>
+    <hyperlink ref="G50" r:id="rId12" xr:uid="{2255613C-CC60-034E-A872-39E0B7FC3D75}"/>
+    <hyperlink ref="G51" r:id="rId13" xr:uid="{7D4BE070-BC2A-F640-AA24-55DB8607633C}"/>
+    <hyperlink ref="G52" r:id="rId14" xr:uid="{62F6C8D0-C319-E24B-82DB-583B28B01D6A}"/>
+    <hyperlink ref="G53" r:id="rId15" xr:uid="{C334E9F0-876C-BF48-B32A-3EF1783AF460}"/>
+    <hyperlink ref="G12" r:id="rId16" xr:uid="{F2BA78C2-850A-4A47-A4F1-5DCF7F273293}"/>
+    <hyperlink ref="G11" r:id="rId17" xr:uid="{436E7BCD-5514-BE44-A962-4391733E23CB}"/>
+    <hyperlink ref="G13" r:id="rId18" xr:uid="{123EFA42-8725-324A-BBCC-6C8EF94E13F0}"/>
+    <hyperlink ref="G14" r:id="rId19" xr:uid="{D3459DF9-68C3-AD4D-8120-D222882E4AD3}"/>
+    <hyperlink ref="G16" r:id="rId20" location="k" xr:uid="{59E1A23C-80ED-2B4F-AFE7-458A4282616D}"/>
+    <hyperlink ref="G17" r:id="rId21" xr:uid="{2CAE0BCF-2A2C-8142-AAFE-6DA57825F133}"/>
+    <hyperlink ref="G30" r:id="rId22" xr:uid="{AA3DA1D0-56F9-4E4C-93C6-CDCFE7FA56E2}"/>
+    <hyperlink ref="G31" r:id="rId23" xr:uid="{0C2EA970-4D01-2748-B88C-3C78E669DCE7}"/>
+    <hyperlink ref="G39" r:id="rId24" xr:uid="{091A8EB7-8C3F-F748-8014-F56861AC0817}"/>
     <hyperlink ref="G2" r:id="rId25" xr:uid="{1E13781E-B861-354C-817E-92F030A541AD}"/>
     <hyperlink ref="G3" r:id="rId26" xr:uid="{2E356582-CD9B-294A-A59D-AE8B3F4EF906}"/>
     <hyperlink ref="G4" r:id="rId27" xr:uid="{D2631B09-11CF-9D49-BC2B-00012E8636BE}"/>
-    <hyperlink ref="G5" r:id="rId28" xr:uid="{F69F7CDE-C350-4540-93FE-EFE72685550A}"/>
-    <hyperlink ref="G7" r:id="rId29" location="gsc.tab=0" xr:uid="{5F9651E1-CC47-9F46-A35D-913CD10FA98B}"/>
-    <hyperlink ref="G6" r:id="rId30" xr:uid="{F67F1519-6345-4847-8D18-FD785616B520}"/>
-    <hyperlink ref="G17" r:id="rId31" xr:uid="{255D97BB-DCE4-A74C-93F3-9E02876D1DEF}"/>
-    <hyperlink ref="G14" r:id="rId32" xr:uid="{571D6DC6-9B82-E444-99A9-0656019A52AA}"/>
-    <hyperlink ref="G8" r:id="rId33" xr:uid="{8C9B77CC-6EB2-FF4D-A768-2BDA18294FE0}"/>
-    <hyperlink ref="G9" r:id="rId34" xr:uid="{BE2C565E-6EE5-3644-8DCD-2FDE7E6A1B7D}"/>
-    <hyperlink ref="G18" r:id="rId35" xr:uid="{283216B3-6D1E-BC47-9A4F-156BCBCEA991}"/>
-    <hyperlink ref="G27" r:id="rId36" xr:uid="{51347FCF-C6E8-A045-84B3-CCBE0B46DD99}"/>
-    <hyperlink ref="G28" r:id="rId37" xr:uid="{1E9157DD-7F86-1D42-8A0B-E535C7309FE9}"/>
+    <hyperlink ref="G6" r:id="rId28" xr:uid="{F69F7CDE-C350-4540-93FE-EFE72685550A}"/>
+    <hyperlink ref="G8" r:id="rId29" location="gsc.tab=0" xr:uid="{5F9651E1-CC47-9F46-A35D-913CD10FA98B}"/>
+    <hyperlink ref="G7" r:id="rId30" xr:uid="{F67F1519-6345-4847-8D18-FD785616B520}"/>
+    <hyperlink ref="G18" r:id="rId31" xr:uid="{255D97BB-DCE4-A74C-93F3-9E02876D1DEF}"/>
+    <hyperlink ref="G15" r:id="rId32" xr:uid="{571D6DC6-9B82-E444-99A9-0656019A52AA}"/>
+    <hyperlink ref="G9" r:id="rId33" xr:uid="{8C9B77CC-6EB2-FF4D-A768-2BDA18294FE0}"/>
+    <hyperlink ref="G10" r:id="rId34" xr:uid="{BE2C565E-6EE5-3644-8DCD-2FDE7E6A1B7D}"/>
+    <hyperlink ref="G19" r:id="rId35" xr:uid="{283216B3-6D1E-BC47-9A4F-156BCBCEA991}"/>
+    <hyperlink ref="G28" r:id="rId36" xr:uid="{51347FCF-C6E8-A045-84B3-CCBE0B46DD99}"/>
+    <hyperlink ref="G29" r:id="rId37" xr:uid="{1E9157DD-7F86-1D42-8A0B-E535C7309FE9}"/>
+    <hyperlink ref="G5" r:id="rId38" xr:uid="{FA848E4A-CAA7-9042-983D-957232FC4890}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
